--- a/Issues.xlsx
+++ b/Issues.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/padmaramaraju/Work/2026-2027/Claude/Projects/CoWork/Lohitas/lohitas-middleware/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/padmaramaraju/Work/2026-2027/Claude/Projects/CoWork/Lohitas/naimix/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{100E3B4F-45F0-DF47-9056-1F20F5D22099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70633AAF-CD21-EB4F-A0F0-6942A9091777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5040" yWindow="1540" windowWidth="27640" windowHeight="16940" activeTab="3" xr2:uid="{C090ABE5-14E0-B34C-911F-B2115D1F2353}"/>
+    <workbookView xWindow="5040" yWindow="1540" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{C090ABE5-14E0-B34C-911F-B2115D1F2353}"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Backend URL must be mandatory for connection</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>Vibe coding enabled with industry standrd tools like Claude and Cursor using the MCP tool</t>
+  </si>
+  <si>
+    <t>Documentation Web Site and jump to documentation from any screen</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CEC5DA-1334-C244-ACE2-BED76F7DED99}">
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52.83203125" customWidth="1"/>
@@ -660,51 +663,56 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>28</v>
       </c>
     </row>

--- a/Issues.xlsx
+++ b/Issues.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/padmaramaraju/Work/2026-2027/Claude/Projects/CoWork/Lohitas/naimix/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70633AAF-CD21-EB4F-A0F0-6942A9091777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4498BE33-6E16-4A47-87F1-6E20C6B7818D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5040" yWindow="1540" windowWidth="27640" windowHeight="16940" activeTab="1" xr2:uid="{C090ABE5-14E0-B34C-911F-B2115D1F2353}"/>
   </bookViews>
@@ -19,7 +19,6 @@
     <sheet name="Foundry vs Lohitas Middleware" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Backend URL must be mandatory for connection</t>
   </si>
@@ -151,13 +150,42 @@
   </si>
   <si>
     <t>Documentation Web Site and jump to documentation from any screen</t>
+  </si>
+  <si>
+    <r>
+      <t>"message"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Monaco"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0451A5"/>
+        <rFont val="Monaco"/>
+        <family val="2"/>
+      </rPr>
+      <t>"This endpoint requires authentication. Log in via POST /auth/login/duende-oauth2-cc and send the returned token as \"Authorization: Bearer &lt;token&gt;\"."</t>
+    </r>
+  </si>
+  <si>
+    <t>Generate MCP for a BFF</t>
+  </si>
+  <si>
+    <t>Configure BFF by linking and grouping end points</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,6 +204,24 @@
       <sz val="14"/>
       <color rgb="FF565959"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Monaco"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFA31515"/>
+      <name val="Monaco"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0451A5"/>
+      <name val="Monaco"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -199,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -210,6 +256,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,7 +627,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CEC5DA-1334-C244-ACE2-BED76F7DED99}">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52.83203125" customWidth="1"/>
@@ -621,99 +668,117 @@
         <v>9</v>
       </c>
     </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2"/>
+    </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>16</v>
+      <c r="A16" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="35" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
